--- a/web/public/forms/gaseol-ultari-sigong.xlsx
+++ b/web/public/forms/gaseol-ultari-sigong.xlsx
@@ -902,7 +902,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
